--- a/data/public.xlsx
+++ b/data/public.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yksok\Documents\GitHub\LegacyR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yksok\Documents\GitHub\LegacyR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{751A18BB-85C8-482E-82BA-B41491D43518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217DA7B1-7622-4EF6-85BD-16574FB1BEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4070" yWindow="120" windowWidth="25210" windowHeight="18360" xr2:uid="{DCE97854-B5D1-43B8-83E7-6CBE2555B87E}"/>
+    <workbookView xWindow="1830" yWindow="800" windowWidth="25210" windowHeight="18360" xr2:uid="{DCE97854-B5D1-43B8-83E7-6CBE2555B87E}"/>
   </bookViews>
   <sheets>
     <sheet name="public" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Days</t>
   </si>
@@ -35,9 +48,6 @@
   </si>
   <si>
     <t>R-R</t>
-  </si>
-  <si>
-    <t>public!$A$2:$A$1000,public!$B$2:$B$1000,public!$E$2:$E$1000</t>
   </si>
   <si>
     <t>Min</t>
@@ -910,10 +920,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CBF4F6-4A43-4C79-B577-AD40C197A3A4}">
-  <dimension ref="A1:H1007"/>
+  <dimension ref="A1:F1007"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -930,7 +940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3</v>
       </c>
@@ -948,7 +958,7 @@
         <v>363.09</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -966,7 +976,7 @@
         <v>122.46000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -984,7 +994,7 @@
         <v>110.94</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1002,7 +1012,7 @@
         <v>198.85000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1020,7 +1030,7 @@
         <v>374.59000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1037,11 +1047,8 @@
         <f t="shared" si="0"/>
         <v>144.60999999999999</v>
       </c>
-      <c r="H7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1059,7 +1066,7 @@
         <v>315.60000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1077,7 +1084,7 @@
         <v>176.97</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1095,7 +1102,7 @@
         <v>442.9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1113,7 +1120,7 @@
         <v>337.11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1131,7 +1138,7 @@
         <v>334.93</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1149,7 +1156,7 @@
         <v>345.82</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1167,7 +1174,7 @@
         <v>184.54000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1185,7 +1192,7 @@
         <v>412.13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
@@ -18952,102 +18959,86 @@
     </row>
     <row r="1004" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1004">
-        <f>MIN(A$2:A$1001)</f>
         <v>1</v>
       </c>
       <c r="B1004">
-        <f t="shared" ref="B1004:E1004" si="16">MIN(B$2:B$1001)</f>
         <v>5</v>
       </c>
       <c r="C1004">
-        <f t="shared" si="16"/>
         <v>1.42</v>
       </c>
       <c r="D1004">
-        <f t="shared" si="16"/>
         <v>117.24</v>
       </c>
       <c r="E1004">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="B1004:E1004" si="16">MIN(E$2:E$1001)</f>
         <v>-1999.4899999999998</v>
       </c>
       <c r="F1004" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1005" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1005">
-        <f>MAX(A$2:A$1001)</f>
         <v>14</v>
       </c>
       <c r="B1005">
-        <f t="shared" ref="B1005:E1005" si="17">MAX(B$2:B$1001)</f>
         <v>1317.07</v>
       </c>
       <c r="C1005">
-        <f t="shared" si="17"/>
         <v>2503.46</v>
       </c>
       <c r="D1005">
-        <f t="shared" si="17"/>
         <v>2337.73</v>
       </c>
       <c r="E1005">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="B1005:E1005" si="17">MAX(E$2:E$1001)</f>
         <v>1519.19</v>
       </c>
       <c r="F1005" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1006">
-        <f>AVERAGE(A$2:A$1001)</f>
         <v>7.0430000000000001</v>
       </c>
       <c r="B1006">
-        <f t="shared" ref="B1006:E1006" si="18">AVERAGE(B$2:B$1001)</f>
         <v>597.41373999999996</v>
       </c>
       <c r="C1006">
-        <f t="shared" si="18"/>
-        <v>1211.0568699999997</v>
+        <v>1211.0568699999999</v>
       </c>
       <c r="D1006">
-        <f t="shared" si="18"/>
-        <v>1349.114029999999</v>
+        <v>1349.11403</v>
       </c>
       <c r="E1006">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="B1006:E1006" si="18">AVERAGE(E$2:E$1001)</f>
         <v>138.05716000000007</v>
       </c>
       <c r="F1006" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1007" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1007">
-        <f>MEDIAN(A$2:A$1001)</f>
         <v>7</v>
       </c>
       <c r="B1007">
-        <f t="shared" ref="B1007:E1007" si="19">MEDIAN(B$2:B$1001)</f>
         <v>621</v>
       </c>
       <c r="C1007">
-        <f t="shared" si="19"/>
         <v>1171.9000000000001</v>
       </c>
       <c r="D1007">
-        <f t="shared" si="19"/>
         <v>1454.26</v>
       </c>
       <c r="E1007">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="B1007:E1007" si="19">MEDIAN(E$2:E$1001)</f>
         <v>233.58500000000004</v>
       </c>
       <c r="F1007" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
